--- a/pca-interpretable-clustering/classified_data/Halide.xlsx
+++ b/pca-interpretable-clustering/classified_data/Halide.xlsx
@@ -4482,7 +4482,7 @@
         <v>7.47555</v>
       </c>
       <c r="H2">
-        <v>85.59139</v>
+        <v>85.59138962</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4508,7 +4508,7 @@
         <v>34.38738</v>
       </c>
       <c r="H3">
-        <v>205.6188</v>
+        <v>205.6187995</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4534,7 +4534,7 @@
         <v>2.8681</v>
       </c>
       <c r="H4">
-        <v>53.37998</v>
+        <v>53.37997664</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4560,7 +4560,7 @@
         <v>9.365869999999999</v>
       </c>
       <c r="H5">
-        <v>81.09757999999999</v>
+        <v>81.09757836</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4586,7 +4586,7 @@
         <v>7.52348</v>
       </c>
       <c r="H6">
-        <v>77.93680999999999</v>
+        <v>77.93681261</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4612,7 +4612,7 @@
         <v>16.46763</v>
       </c>
       <c r="H7">
-        <v>198.30976</v>
+        <v>198.309761</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4638,7 +4638,7 @@
         <v>95.87788999999999</v>
       </c>
       <c r="H8">
-        <v>322.7503</v>
+        <v>341.9134954</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4664,7 +4664,7 @@
         <v>84.33302</v>
       </c>
       <c r="H9">
-        <v>350.6383</v>
+        <v>350.6382983</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4690,7 +4690,7 @@
         <v>13.4844</v>
       </c>
       <c r="H10">
-        <v>119.61244</v>
+        <v>119.6124402</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4716,7 +4716,7 @@
         <v>10.66649</v>
       </c>
       <c r="H11">
-        <v>139.09762</v>
+        <v>139.0976242</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4742,7 +4742,7 @@
         <v>1.80957</v>
       </c>
       <c r="H12">
-        <v>61.55038</v>
+        <v>61.55038421</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4768,7 +4768,7 @@
         <v>9.400969999999999</v>
       </c>
       <c r="H13">
-        <v>97.35057</v>
+        <v>97.35057433999999</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4794,7 +4794,7 @@
         <v>26.004</v>
       </c>
       <c r="H14">
-        <v>216.71082</v>
+        <v>216.7108179</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4820,7 +4820,7 @@
         <v>4.70954</v>
       </c>
       <c r="H15">
-        <v>117.20862</v>
+        <v>117.2086183</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4846,7 +4846,7 @@
         <v>4.63003</v>
       </c>
       <c r="H16">
-        <v>56.00884</v>
+        <v>56.00883809</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4872,7 +4872,7 @@
         <v>28.45061</v>
       </c>
       <c r="H17">
-        <v>203.36345</v>
+        <v>259.6340762</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4898,7 +4898,7 @@
         <v>7.01367</v>
       </c>
       <c r="H18">
-        <v>88.31695999999999</v>
+        <v>88.31696298999999</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4924,7 +4924,7 @@
         <v>8.37501</v>
       </c>
       <c r="H19">
-        <v>121.86201</v>
+        <v>121.8620059</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4950,7 +4950,7 @@
         <v>1.01004</v>
       </c>
       <c r="H20">
-        <v>36.95402</v>
+        <v>36.95402368</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4976,7 +4976,7 @@
         <v>1.74257</v>
       </c>
       <c r="H21">
-        <v>41.6686</v>
+        <v>41.66860085</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -5002,7 +5002,7 @@
         <v>4.50285</v>
       </c>
       <c r="H22">
-        <v>60.25009</v>
+        <v>60.2500945</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -5028,7 +5028,7 @@
         <v>70.07129999999999</v>
       </c>
       <c r="H23">
-        <v>346.56827</v>
+        <v>346.5682748</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -5054,7 +5054,7 @@
         <v>11.8151</v>
       </c>
       <c r="H24">
-        <v>124.8023</v>
+        <v>124.8022976</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -5080,7 +5080,7 @@
         <v>15.7923</v>
       </c>
       <c r="H25">
-        <v>126.57492</v>
+        <v>126.5749192</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -5106,7 +5106,7 @@
         <v>9.4468</v>
       </c>
       <c r="H26">
-        <v>83.67326</v>
+        <v>150.9034824</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -5132,7 +5132,7 @@
         <v>71.34477</v>
       </c>
       <c r="H27">
-        <v>451.7357</v>
+        <v>451.735701</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -5158,7 +5158,7 @@
         <v>0.44303</v>
       </c>
       <c r="H28">
-        <v>33.263</v>
+        <v>33.26300356</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -5184,7 +5184,7 @@
         <v>60.15137</v>
       </c>
       <c r="H29">
-        <v>272.27316</v>
+        <v>272.273159</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -5210,7 +5210,7 @@
         <v>5.41575</v>
       </c>
       <c r="H30">
-        <v>138.61111</v>
+        <v>138.6111117</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5236,7 +5236,7 @@
         <v>73.59554</v>
       </c>
       <c r="H31">
-        <v>511.12932</v>
+        <v>511.129316</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5262,7 +5262,7 @@
         <v>4.23562</v>
       </c>
       <c r="H32">
-        <v>62.08052</v>
+        <v>62.08051574</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -5288,7 +5288,7 @@
         <v>0.78683</v>
       </c>
       <c r="H33">
-        <v>39.11232</v>
+        <v>39.11231787</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -5314,7 +5314,7 @@
         <v>17.86387</v>
       </c>
       <c r="H34">
-        <v>173.61056</v>
+        <v>173.6105606</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -5340,7 +5340,7 @@
         <v>41.9428</v>
       </c>
       <c r="H35">
-        <v>208.44413</v>
+        <v>208.4441272</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -5366,7 +5366,7 @@
         <v>18.5893</v>
       </c>
       <c r="H36">
-        <v>120.81214</v>
+        <v>120.8121405</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -5392,7 +5392,7 @@
         <v>9.53045</v>
       </c>
       <c r="H37">
-        <v>138.89577</v>
+        <v>138.8957707</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5418,7 +5418,7 @@
         <v>62.49686</v>
       </c>
       <c r="H38">
-        <v>292.49613</v>
+        <v>292.4961267</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -5444,7 +5444,7 @@
         <v>2.30339</v>
       </c>
       <c r="H39">
-        <v>88.06674</v>
+        <v>88.06673777</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5470,7 +5470,7 @@
         <v>28.4981</v>
       </c>
       <c r="H40">
-        <v>175.51717</v>
+        <v>175.5171684</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5496,7 +5496,7 @@
         <v>20.1852</v>
       </c>
       <c r="H41">
-        <v>175.77211</v>
+        <v>175.7721076</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -5522,7 +5522,7 @@
         <v>48.3537</v>
       </c>
       <c r="H42">
-        <v>285.93274</v>
+        <v>285.9327448</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5548,7 +5548,7 @@
         <v>49.45208</v>
       </c>
       <c r="H43">
-        <v>237.04403</v>
+        <v>237.0440292</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5574,7 +5574,7 @@
         <v>0.52884</v>
       </c>
       <c r="H44">
-        <v>35.66911</v>
+        <v>35.66911192</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -5600,7 +5600,7 @@
         <v>5.6595</v>
       </c>
       <c r="H45">
-        <v>101.06763</v>
+        <v>101.0676272</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -5626,7 +5626,7 @@
         <v>29.44403</v>
       </c>
       <c r="H46">
-        <v>455.687</v>
+        <v>455.6869972</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5652,7 +5652,7 @@
         <v>10.3501</v>
       </c>
       <c r="H47">
-        <v>84.4545</v>
+        <v>84.45449881</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5678,7 +5678,7 @@
         <v>26.44205</v>
       </c>
       <c r="H48">
-        <v>182.77174</v>
+        <v>158.6154719</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -5704,7 +5704,7 @@
         <v>13.61776</v>
       </c>
       <c r="H49">
-        <v>105.84542</v>
+        <v>105.8454168</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -5730,7 +5730,7 @@
         <v>13.22012</v>
       </c>
       <c r="H50">
-        <v>106.7209</v>
+        <v>106.720902</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -5756,7 +5756,7 @@
         <v>6.30184</v>
       </c>
       <c r="H51">
-        <v>80.87036999999999</v>
+        <v>80.87037109000001</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -5782,7 +5782,7 @@
         <v>29.75539</v>
       </c>
       <c r="H52">
-        <v>195.13332</v>
+        <v>195.1333162</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -5808,7 +5808,7 @@
         <v>8.476330000000001</v>
       </c>
       <c r="H53">
-        <v>97.96502</v>
+        <v>97.96501657</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -5834,7 +5834,7 @@
         <v>79.91173999999999</v>
       </c>
       <c r="H54">
-        <v>277.59182</v>
+        <v>306.0257831</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -5860,7 +5860,7 @@
         <v>20.9576</v>
       </c>
       <c r="H55">
-        <v>132.40835</v>
+        <v>126.4141014</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -5886,7 +5886,7 @@
         <v>32.77773</v>
       </c>
       <c r="H56">
-        <v>177.88952</v>
+        <v>154.06425</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -5912,7 +5912,7 @@
         <v>15.89985</v>
       </c>
       <c r="H57">
-        <v>104.28987</v>
+        <v>101.0745009</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5938,7 +5938,7 @@
         <v>22.81818</v>
       </c>
       <c r="H58">
-        <v>145.18412</v>
+        <v>145.1841223</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -5964,7 +5964,7 @@
         <v>59.93071</v>
       </c>
       <c r="H59">
-        <v>286.12033</v>
+        <v>286.1203283</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5990,7 +5990,7 @@
         <v>110.78566</v>
       </c>
       <c r="H60">
-        <v>347.73109</v>
+        <v>370.0116429</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -6016,7 +6016,7 @@
         <v>14.27349</v>
       </c>
       <c r="H61">
-        <v>104.19202</v>
+        <v>97.31867228</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -6042,7 +6042,7 @@
         <v>11.95056</v>
       </c>
       <c r="H62">
-        <v>88.08656999999999</v>
+        <v>79.04697428</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -6068,7 +6068,7 @@
         <v>5.44236</v>
       </c>
       <c r="H63">
-        <v>63.51591</v>
+        <v>63.51590859</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -6094,7 +6094,7 @@
         <v>29.22046</v>
       </c>
       <c r="H64">
-        <v>172.23051</v>
+        <v>172.2305091</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -6120,7 +6120,7 @@
         <v>106.7895</v>
       </c>
       <c r="H65">
-        <v>343.26119</v>
+        <v>376.0184608</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -6146,7 +6146,7 @@
         <v>7.27514</v>
       </c>
       <c r="H66">
-        <v>104.81962</v>
+        <v>104.8196181</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -6172,7 +6172,7 @@
         <v>19.32727</v>
       </c>
       <c r="H67">
-        <v>157.35948</v>
+        <v>132.2125312</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -6198,7 +6198,7 @@
         <v>104.2965</v>
       </c>
       <c r="H68">
-        <v>546.7838400000001</v>
+        <v>546.7838408</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -6224,7 +6224,7 @@
         <v>79.16801</v>
       </c>
       <c r="H69">
-        <v>400.35863</v>
+        <v>321.3107049</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -6250,7 +6250,7 @@
         <v>8.094340000000001</v>
       </c>
       <c r="H70">
-        <v>110.30317</v>
+        <v>110.3031678</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -6276,7 +6276,7 @@
         <v>6.61694</v>
       </c>
       <c r="H71">
-        <v>97.04911</v>
+        <v>97.049114</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -6302,7 +6302,7 @@
         <v>3.16632</v>
       </c>
       <c r="H72">
-        <v>71.93817</v>
+        <v>71.93816825</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -6328,7 +6328,7 @@
         <v>9.64608</v>
       </c>
       <c r="H73">
-        <v>100.25279</v>
+        <v>100.252788</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -6354,7 +6354,7 @@
         <v>126.87334</v>
       </c>
       <c r="H74">
-        <v>383.85332</v>
+        <v>355.8281828</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -6380,7 +6380,7 @@
         <v>4.04882</v>
       </c>
       <c r="H75">
-        <v>60.0389</v>
+        <v>60.03890428</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -6406,7 +6406,7 @@
         <v>119.35008</v>
       </c>
       <c r="H76">
-        <v>362.06411</v>
+        <v>365.3788134</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -6432,7 +6432,7 @@
         <v>17.68496</v>
       </c>
       <c r="H77">
-        <v>119.67684</v>
+        <v>108.3353996</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -6458,7 +6458,7 @@
         <v>6.78888</v>
       </c>
       <c r="H78">
-        <v>96.61887</v>
+        <v>96.61886962</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -6484,7 +6484,7 @@
         <v>38.28427</v>
       </c>
       <c r="H79">
-        <v>183.78728</v>
+        <v>194.3062384</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -6510,7 +6510,7 @@
         <v>9.941509999999999</v>
       </c>
       <c r="H80">
-        <v>106.74623</v>
+        <v>106.7462297</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -6536,7 +6536,7 @@
         <v>2.8829</v>
       </c>
       <c r="H81">
-        <v>51.75104</v>
+        <v>51.75103703</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -6562,7 +6562,7 @@
         <v>17.99935</v>
       </c>
       <c r="H82">
-        <v>124.73877</v>
+        <v>88.3430192</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -6588,7 +6588,7 @@
         <v>18.8513</v>
       </c>
       <c r="H83">
-        <v>117.61407</v>
+        <v>83.31979382999999</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -6614,7 +6614,7 @@
         <v>9.7151</v>
       </c>
       <c r="H84">
-        <v>83.41254000000001</v>
+        <v>130.0002527</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -6640,7 +6640,7 @@
         <v>13.64368</v>
       </c>
       <c r="H85">
-        <v>110.20433</v>
+        <v>110.2043336</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -6666,7 +6666,7 @@
         <v>13.31742</v>
       </c>
       <c r="H86">
-        <v>107.29974</v>
+        <v>165.0656632</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -6692,7 +6692,7 @@
         <v>26.13451</v>
       </c>
       <c r="H87">
-        <v>229.73943</v>
+        <v>229.7394344</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -6718,7 +6718,7 @@
         <v>3.54081</v>
       </c>
       <c r="H88">
-        <v>50.0423</v>
+        <v>50.04230099</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -6744,7 +6744,7 @@
         <v>16.81622</v>
       </c>
       <c r="H89">
-        <v>145.11746</v>
+        <v>145.117464</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -6796,7 +6796,7 @@
         <v>6.3968</v>
       </c>
       <c r="H91">
-        <v>74.98817</v>
+        <v>74.98816739999999</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6822,7 +6822,7 @@
         <v>4.48107</v>
       </c>
       <c r="H92">
-        <v>83.75270999999999</v>
+        <v>83.75271026</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -6848,7 +6848,7 @@
         <v>100.57211</v>
       </c>
       <c r="H93">
-        <v>541.23316</v>
+        <v>541.2331593</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -6874,7 +6874,7 @@
         <v>13.86051</v>
       </c>
       <c r="H94">
-        <v>96.37779999999999</v>
+        <v>96.60421717</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -6900,7 +6900,7 @@
         <v>12.37235</v>
       </c>
       <c r="H95">
-        <v>102.30717</v>
+        <v>102.3071696</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -6926,7 +6926,7 @@
         <v>25.11412</v>
       </c>
       <c r="H96">
-        <v>186.94736</v>
+        <v>186.9473571</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -6952,7 +6952,7 @@
         <v>45.21161</v>
       </c>
       <c r="H97">
-        <v>254.75511</v>
+        <v>254.7551128</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -6978,7 +6978,7 @@
         <v>27.10886</v>
       </c>
       <c r="H98">
-        <v>187.01719</v>
+        <v>187.0171889</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -7004,7 +7004,7 @@
         <v>72.05448</v>
       </c>
       <c r="H99">
-        <v>297.61117</v>
+        <v>297.6111702</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -7030,7 +7030,7 @@
         <v>84.10578</v>
       </c>
       <c r="H100">
-        <v>415.11039</v>
+        <v>415.110391</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -7056,7 +7056,7 @@
         <v>34.14197</v>
       </c>
       <c r="H101">
-        <v>228.85245</v>
+        <v>228.8524507</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -7082,7 +7082,7 @@
         <v>24.0119</v>
       </c>
       <c r="H102">
-        <v>133.38352</v>
+        <v>157.1493403</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -7108,7 +7108,7 @@
         <v>27.59646</v>
       </c>
       <c r="H103">
-        <v>169.27576</v>
+        <v>227.0464956</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -7134,7 +7134,7 @@
         <v>15.44004</v>
       </c>
       <c r="H104">
-        <v>176.59916</v>
+        <v>176.599161</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -7160,7 +7160,7 @@
         <v>13.89599</v>
       </c>
       <c r="H105">
-        <v>153.54344</v>
+        <v>153.5434387</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -7186,7 +7186,7 @@
         <v>19.83961</v>
       </c>
       <c r="H106">
-        <v>260.64652</v>
+        <v>260.6465152</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -7212,7 +7212,7 @@
         <v>12.9886</v>
       </c>
       <c r="H107">
-        <v>98.2405</v>
+        <v>88.92893737</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -7238,7 +7238,7 @@
         <v>21.1789</v>
       </c>
       <c r="H108">
-        <v>123.25633</v>
+        <v>123.2563316</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -7264,7 +7264,7 @@
         <v>121.70918</v>
       </c>
       <c r="H109">
-        <v>374.12352</v>
+        <v>340.7536282</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -7290,7 +7290,7 @@
         <v>13.19948</v>
       </c>
       <c r="H110">
-        <v>156.55721</v>
+        <v>192.6468421</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -7316,7 +7316,7 @@
         <v>34.95632</v>
       </c>
       <c r="H111">
-        <v>304.35665</v>
+        <v>304.3566469</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -7342,7 +7342,7 @@
         <v>14.29061</v>
       </c>
       <c r="H112">
-        <v>130.78566</v>
+        <v>130.7856579</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -7368,7 +7368,7 @@
         <v>17.11233</v>
       </c>
       <c r="H113">
-        <v>173.79753</v>
+        <v>173.7975304</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -7394,7 +7394,7 @@
         <v>16.88591</v>
       </c>
       <c r="H114">
-        <v>152.77759</v>
+        <v>152.7775865</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -7420,7 +7420,7 @@
         <v>15.70957</v>
       </c>
       <c r="H115">
-        <v>150.17578</v>
+        <v>150.1757801</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -7446,7 +7446,7 @@
         <v>16.2323</v>
       </c>
       <c r="H116">
-        <v>119.07994</v>
+        <v>207.9582321</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -7472,7 +7472,7 @@
         <v>60.54651</v>
       </c>
       <c r="H117">
-        <v>358.30249</v>
+        <v>338.2575332</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -7498,7 +7498,7 @@
         <v>22.08688</v>
       </c>
       <c r="H118">
-        <v>201.72174</v>
+        <v>201.7217415</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -7524,7 +7524,7 @@
         <v>42.90942</v>
       </c>
       <c r="H119">
-        <v>203.72687</v>
+        <v>185.0204561</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -7550,7 +7550,7 @@
         <v>48.11979</v>
       </c>
       <c r="H120">
-        <v>236.14575</v>
+        <v>224.6549873</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -7576,7 +7576,7 @@
         <v>38.29462</v>
       </c>
       <c r="H121">
-        <v>186.96607</v>
+        <v>197.593544</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -7602,7 +7602,7 @@
         <v>117.78792</v>
       </c>
       <c r="H122">
-        <v>356.34153</v>
+        <v>356.3415311</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -7628,7 +7628,7 @@
         <v>148.20775</v>
       </c>
       <c r="H123">
-        <v>365.01095</v>
+        <v>365.0109499</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -7654,7 +7654,7 @@
         <v>12.28814</v>
       </c>
       <c r="H124">
-        <v>111.78038</v>
+        <v>138.0629568</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -7680,7 +7680,7 @@
         <v>60.30539</v>
       </c>
       <c r="H125">
-        <v>247.42683</v>
+        <v>247.4268273</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -7706,7 +7706,7 @@
         <v>129.9135</v>
       </c>
       <c r="H126">
-        <v>352.71124</v>
+        <v>352.711243</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -7732,7 +7732,7 @@
         <v>13.90471</v>
       </c>
       <c r="H127">
-        <v>193.74492</v>
+        <v>193.7449218</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -7758,7 +7758,7 @@
         <v>145.89184</v>
       </c>
       <c r="H128">
-        <v>364.1214</v>
+        <v>364.1214022</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -7784,7 +7784,7 @@
         <v>110.21387</v>
       </c>
       <c r="H129">
-        <v>345.79426</v>
+        <v>272.1715839</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -7810,7 +7810,7 @@
         <v>126.5244</v>
       </c>
       <c r="H130">
-        <v>363.18759</v>
+        <v>363.1875852</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -7836,7 +7836,7 @@
         <v>111.75083</v>
       </c>
       <c r="H131">
-        <v>310.77288</v>
+        <v>310.7728778</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -7862,7 +7862,7 @@
         <v>21.58178</v>
       </c>
       <c r="H132">
-        <v>265.56587</v>
+        <v>265.5658722</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -7888,7 +7888,7 @@
         <v>45.3757</v>
       </c>
       <c r="H133">
-        <v>189.95892</v>
+        <v>189.9589243</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7914,7 +7914,7 @@
         <v>122.2312</v>
       </c>
       <c r="H134">
-        <v>361.26799</v>
+        <v>361.2679938</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -7940,7 +7940,7 @@
         <v>72.77148</v>
       </c>
       <c r="H135">
-        <v>237.17423</v>
+        <v>237.1742285</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -7966,7 +7966,7 @@
         <v>132.58265</v>
       </c>
       <c r="H136">
-        <v>364.01102</v>
+        <v>281.5968087</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7992,7 +7992,7 @@
         <v>142.26379</v>
       </c>
       <c r="H137">
-        <v>366.72659</v>
+        <v>278.5131669</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -8018,7 +8018,7 @@
         <v>46.72967</v>
       </c>
       <c r="H138">
-        <v>234.95626</v>
+        <v>211.1675041</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -8044,7 +8044,7 @@
         <v>60.13485</v>
       </c>
       <c r="H139">
-        <v>298.86711</v>
+        <v>271.703558</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -8070,7 +8070,7 @@
         <v>84.24843</v>
       </c>
       <c r="H140">
-        <v>333.23867</v>
+        <v>333.2386684</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -8096,7 +8096,7 @@
         <v>56.03267</v>
       </c>
       <c r="H141">
-        <v>310.57535</v>
+        <v>310.5753502</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -8122,7 +8122,7 @@
         <v>14.41144</v>
       </c>
       <c r="H142">
-        <v>130.0062</v>
+        <v>130.0061957</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -8148,7 +8148,7 @@
         <v>20.11123</v>
       </c>
       <c r="H143">
-        <v>147.42107</v>
+        <v>147.4210712</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -8174,7 +8174,7 @@
         <v>138.63081</v>
       </c>
       <c r="H144">
-        <v>442.70128</v>
+        <v>442.7012827</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -8200,7 +8200,7 @@
         <v>33.11261</v>
       </c>
       <c r="H145">
-        <v>149.96628</v>
+        <v>149.9662784</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -8226,7 +8226,7 @@
         <v>77.46124</v>
       </c>
       <c r="H146">
-        <v>483.02095</v>
+        <v>483.0209509</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -8252,7 +8252,7 @@
         <v>129.81683</v>
       </c>
       <c r="H147">
-        <v>605.44019</v>
+        <v>605.4401932</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -8278,7 +8278,7 @@
         <v>94.67932</v>
       </c>
       <c r="H148">
-        <v>399.19969</v>
+        <v>349.6163214</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -8304,7 +8304,7 @@
         <v>6.00813</v>
       </c>
       <c r="H149">
-        <v>62.35351</v>
+        <v>62.35351024</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -8330,7 +8330,7 @@
         <v>93.34943</v>
       </c>
       <c r="H150">
-        <v>279.66492</v>
+        <v>279.6649176</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -8356,7 +8356,7 @@
         <v>29.2221</v>
       </c>
       <c r="H151">
-        <v>148.73449</v>
+        <v>148.7344943</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -8382,7 +8382,7 @@
         <v>17.14349</v>
       </c>
       <c r="H152">
-        <v>131.39203</v>
+        <v>130.1092649</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -8408,7 +8408,7 @@
         <v>22.21951</v>
       </c>
       <c r="H153">
-        <v>172.87516</v>
+        <v>162.6751469</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -8434,7 +8434,7 @@
         <v>38.34282</v>
       </c>
       <c r="H154">
-        <v>224.9726</v>
+        <v>251.6152351</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -8460,7 +8460,7 @@
         <v>19.77114</v>
       </c>
       <c r="H155">
-        <v>156.38606</v>
+        <v>156.3860581</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -8486,7 +8486,7 @@
         <v>28.59193</v>
       </c>
       <c r="H156">
-        <v>184.68033</v>
+        <v>184.6803302</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -8512,7 +8512,7 @@
         <v>28.07238</v>
       </c>
       <c r="H157">
-        <v>161.77278</v>
+        <v>225.1907759</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -8538,7 +8538,7 @@
         <v>20.1422</v>
       </c>
       <c r="H158">
-        <v>157.89781</v>
+        <v>157.8978117</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -8564,7 +8564,7 @@
         <v>13.6994</v>
       </c>
       <c r="H159">
-        <v>106.20156</v>
+        <v>126.5818335</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -8590,7 +8590,7 @@
         <v>11.52473</v>
       </c>
       <c r="H160">
-        <v>93.04532</v>
+        <v>93.04531953</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -8616,7 +8616,7 @@
         <v>12.88484</v>
       </c>
       <c r="H161">
-        <v>110.39453</v>
+        <v>110.3945339</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -8642,7 +8642,7 @@
         <v>14.92913</v>
       </c>
       <c r="H162">
-        <v>94.69848</v>
+        <v>119.8433523</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -8668,7 +8668,7 @@
         <v>14.56526</v>
       </c>
       <c r="H163">
-        <v>100.02249</v>
+        <v>185.9246633</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -8694,7 +8694,7 @@
         <v>31.36635</v>
       </c>
       <c r="H164">
-        <v>140.22683</v>
+        <v>140.2268327</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -8720,7 +8720,7 @@
         <v>11.86598</v>
       </c>
       <c r="H165">
-        <v>79.70722000000001</v>
+        <v>100.1704389</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -8746,7 +8746,7 @@
         <v>27.51242</v>
       </c>
       <c r="H166">
-        <v>248.7482</v>
+        <v>248.7482034</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -8798,7 +8798,7 @@
         <v>53.85099</v>
       </c>
       <c r="H168">
-        <v>333.5946</v>
+        <v>333.5945953</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -8824,7 +8824,7 @@
         <v>20.65301</v>
       </c>
       <c r="H169">
-        <v>122.61925</v>
+        <v>158.552133</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -8850,7 +8850,7 @@
         <v>51.60667</v>
       </c>
       <c r="H170">
-        <v>290.88198</v>
+        <v>290.8819838</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -8876,7 +8876,7 @@
         <v>56.30449</v>
       </c>
       <c r="H171">
-        <v>261.65703</v>
+        <v>261.6570294</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -8902,7 +8902,7 @@
         <v>125.72717</v>
       </c>
       <c r="H172">
-        <v>375.68398</v>
+        <v>375.6839848</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -8928,7 +8928,7 @@
         <v>41.60671</v>
       </c>
       <c r="H173">
-        <v>249.67824</v>
+        <v>249.6782391</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -8954,7 +8954,7 @@
         <v>29.96465</v>
       </c>
       <c r="H174">
-        <v>181.13389</v>
+        <v>181.1338879</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -8980,7 +8980,7 @@
         <v>53.55641</v>
       </c>
       <c r="H175">
-        <v>303.86012</v>
+        <v>303.8601151</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -9006,7 +9006,7 @@
         <v>23.60849</v>
       </c>
       <c r="H176">
-        <v>189.13842</v>
+        <v>189.1384155</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -9032,7 +9032,7 @@
         <v>46.3673</v>
       </c>
       <c r="H177">
-        <v>263.91812</v>
+        <v>263.918117</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -9058,7 +9058,7 @@
         <v>73.99203</v>
       </c>
       <c r="H178">
-        <v>358.32573</v>
+        <v>358.325734</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -9084,7 +9084,7 @@
         <v>25.0131</v>
       </c>
       <c r="H179">
-        <v>143.03747</v>
+        <v>143.0374741</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -9110,7 +9110,7 @@
         <v>108.06134</v>
       </c>
       <c r="H180">
-        <v>320.4049</v>
+        <v>320.4048988</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -9136,7 +9136,7 @@
         <v>89.34487</v>
       </c>
       <c r="H181">
-        <v>424.21981</v>
+        <v>424.2198132</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -9162,7 +9162,7 @@
         <v>85.42116</v>
       </c>
       <c r="H182">
-        <v>346.75699</v>
+        <v>346.7569939</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -9188,7 +9188,7 @@
         <v>41.28074</v>
       </c>
       <c r="H183">
-        <v>224.42384</v>
+        <v>224.4238423</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -9214,7 +9214,7 @@
         <v>15.52577</v>
       </c>
       <c r="H184">
-        <v>137.57756</v>
+        <v>137.5775604</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -9240,7 +9240,7 @@
         <v>21.38018</v>
       </c>
       <c r="H185">
-        <v>184.11394</v>
+        <v>184.1139398</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -9266,7 +9266,7 @@
         <v>28.42505</v>
       </c>
       <c r="H186">
-        <v>226.56321</v>
+        <v>226.5632054</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -9292,7 +9292,7 @@
         <v>26.72822</v>
       </c>
       <c r="H187">
-        <v>186.55831</v>
+        <v>186.5583142</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -9344,7 +9344,7 @@
         <v>34.68436</v>
       </c>
       <c r="H189">
-        <v>333.59801</v>
+        <v>333.5980092</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -9370,7 +9370,7 @@
         <v>28.14812</v>
       </c>
       <c r="H190">
-        <v>242.88133</v>
+        <v>242.8813312</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -9396,7 +9396,7 @@
         <v>62.51124</v>
       </c>
       <c r="H191">
-        <v>296.32465</v>
+        <v>296.3246497</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -9422,7 +9422,7 @@
         <v>20.98159</v>
       </c>
       <c r="H192">
-        <v>104.34878</v>
+        <v>104.3487768</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -9448,7 +9448,7 @@
         <v>6.86444</v>
       </c>
       <c r="H193">
-        <v>66.60263</v>
+        <v>66.60262822999999</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -9474,7 +9474,7 @@
         <v>85.3814</v>
       </c>
       <c r="H194">
-        <v>343.64682</v>
+        <v>343.6468174</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -9500,7 +9500,7 @@
         <v>6.23918</v>
       </c>
       <c r="H195">
-        <v>72.41416</v>
+        <v>126.1600797</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -9526,7 +9526,7 @@
         <v>4.7034</v>
       </c>
       <c r="H196">
-        <v>56.63844</v>
+        <v>94.22765665999999</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -9552,7 +9552,7 @@
         <v>30.8854</v>
       </c>
       <c r="H197">
-        <v>248.22692</v>
+        <v>248.2269231</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -9578,7 +9578,7 @@
         <v>29.2875</v>
       </c>
       <c r="H198">
-        <v>210.70664</v>
+        <v>210.7066448</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -9604,7 +9604,7 @@
         <v>25.46746</v>
       </c>
       <c r="H199">
-        <v>204.81901</v>
+        <v>204.8190141</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -9630,7 +9630,7 @@
         <v>26.76931</v>
       </c>
       <c r="H200">
-        <v>173.9853</v>
+        <v>173.9853001</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -9656,7 +9656,7 @@
         <v>50.29134</v>
       </c>
       <c r="H201">
-        <v>266.62291</v>
+        <v>361.4700881</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -9682,7 +9682,7 @@
         <v>9.94097</v>
       </c>
       <c r="H202">
-        <v>106.6105</v>
+        <v>106.6104983</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -9708,7 +9708,7 @@
         <v>13.94702</v>
       </c>
       <c r="H203">
-        <v>167.35621</v>
+        <v>167.3562078</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -9734,7 +9734,7 @@
         <v>12.88642</v>
       </c>
       <c r="H204">
-        <v>138.88692</v>
+        <v>138.8869192</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -9760,7 +9760,7 @@
         <v>21.84554</v>
       </c>
       <c r="H205">
-        <v>160.51283</v>
+        <v>160.5128277</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -9786,7 +9786,7 @@
         <v>19.54668</v>
       </c>
       <c r="H206">
-        <v>226.08867</v>
+        <v>226.0886703</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -9812,7 +9812,7 @@
         <v>44.32926</v>
       </c>
       <c r="H207">
-        <v>266.42411</v>
+        <v>266.4241125</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -9838,7 +9838,7 @@
         <v>54.43377</v>
       </c>
       <c r="H208">
-        <v>336.16481</v>
+        <v>336.1648052</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -9864,7 +9864,7 @@
         <v>48.63726</v>
       </c>
       <c r="H209">
-        <v>328.44612</v>
+        <v>328.4461221</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -9890,7 +9890,7 @@
         <v>4.83863</v>
       </c>
       <c r="H210">
-        <v>62.813</v>
+        <v>62.81300199</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -9916,7 +9916,7 @@
         <v>17.97098</v>
       </c>
       <c r="H211">
-        <v>184.89785</v>
+        <v>184.8978481</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -9942,7 +9942,7 @@
         <v>16.61213</v>
       </c>
       <c r="H212">
-        <v>148.85359</v>
+        <v>148.8535922</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -9968,7 +9968,7 @@
         <v>5.18497</v>
       </c>
       <c r="H213">
-        <v>63.43709</v>
+        <v>63.43708632</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -9994,7 +9994,7 @@
         <v>7.96424</v>
       </c>
       <c r="H214">
-        <v>131.07715</v>
+        <v>131.0771474</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -10020,7 +10020,7 @@
         <v>23.25436</v>
       </c>
       <c r="H215">
-        <v>169.43057</v>
+        <v>169.4305735</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -10046,7 +10046,7 @@
         <v>33.14024</v>
       </c>
       <c r="H216">
-        <v>260.27851</v>
+        <v>260.2785124</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -10072,7 +10072,7 @@
         <v>1.42336</v>
       </c>
       <c r="H217">
-        <v>45.28878</v>
+        <v>45.28878497</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -10098,7 +10098,7 @@
         <v>38.45572</v>
       </c>
       <c r="H218">
-        <v>232.23679</v>
+        <v>232.2367882</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -10124,7 +10124,7 @@
         <v>54.87648</v>
       </c>
       <c r="H219">
-        <v>306.37787</v>
+        <v>398.686814</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -10150,7 +10150,7 @@
         <v>49.25825</v>
       </c>
       <c r="H220">
-        <v>255.34347</v>
+        <v>255.3434717</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -10176,7 +10176,7 @@
         <v>50.09906</v>
       </c>
       <c r="H221">
-        <v>295.55327</v>
+        <v>295.5532714</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -10202,7 +10202,7 @@
         <v>44.13486</v>
       </c>
       <c r="H222">
-        <v>283.72072</v>
+        <v>283.720724</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -10228,7 +10228,7 @@
         <v>67.64288000000001</v>
       </c>
       <c r="H223">
-        <v>310.239</v>
+        <v>310.239002</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -10254,7 +10254,7 @@
         <v>11.35818</v>
       </c>
       <c r="H224">
-        <v>86.54908</v>
+        <v>116.2345368</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -10280,7 +10280,7 @@
         <v>11.26058</v>
       </c>
       <c r="H225">
-        <v>83.93078</v>
+        <v>103.2576723</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -10306,7 +10306,7 @@
         <v>8.171799999999999</v>
       </c>
       <c r="H226">
-        <v>77.18738</v>
+        <v>77.18737523999999</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -10332,7 +10332,7 @@
         <v>19.71008</v>
       </c>
       <c r="H227">
-        <v>142.1421</v>
+        <v>142.1420964</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -10358,7 +10358,7 @@
         <v>28.92512</v>
       </c>
       <c r="H228">
-        <v>206.91421</v>
+        <v>206.9142131</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -10384,7 +10384,7 @@
         <v>93.92026</v>
       </c>
       <c r="H229">
-        <v>519.16016</v>
+        <v>478.4358993</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -10410,7 +10410,7 @@
         <v>17.17666</v>
       </c>
       <c r="H230">
-        <v>152.64572</v>
+        <v>152.6457217</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -10436,7 +10436,7 @@
         <v>51.09143</v>
       </c>
       <c r="H231">
-        <v>200.13595</v>
+        <v>186.8423449</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -10462,7 +10462,7 @@
         <v>6.18444</v>
       </c>
       <c r="H232">
-        <v>78.14156</v>
+        <v>150.4321458</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -10514,7 +10514,7 @@
         <v>24.88464</v>
       </c>
       <c r="H234">
-        <v>190.5035</v>
+        <v>190.5035028</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -10540,7 +10540,7 @@
         <v>24.8834</v>
       </c>
       <c r="H235">
-        <v>181.52843</v>
+        <v>181.5284315</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -10566,7 +10566,7 @@
         <v>20.07813</v>
       </c>
       <c r="H236">
-        <v>147.68765</v>
+        <v>147.6876472</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -10592,7 +10592,7 @@
         <v>10.92499</v>
       </c>
       <c r="H237">
-        <v>96.67843000000001</v>
+        <v>120.9614942</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -10618,7 +10618,7 @@
         <v>22.6975</v>
       </c>
       <c r="H238">
-        <v>169.78374</v>
+        <v>169.783736</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -10644,7 +10644,7 @@
         <v>23.68753</v>
       </c>
       <c r="H239">
-        <v>179.17608</v>
+        <v>179.1760781</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -10670,7 +10670,7 @@
         <v>11.84826</v>
       </c>
       <c r="H240">
-        <v>98.86439</v>
+        <v>98.86439102</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -10696,7 +10696,7 @@
         <v>13.60383</v>
       </c>
       <c r="H241">
-        <v>157.11807</v>
+        <v>157.1180705</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -10722,7 +10722,7 @@
         <v>14.86248</v>
       </c>
       <c r="H242">
-        <v>110.86796</v>
+        <v>110.8679605</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -10748,7 +10748,7 @@
         <v>24.75642</v>
       </c>
       <c r="H243">
-        <v>217.57481</v>
+        <v>217.5748143</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -10774,7 +10774,7 @@
         <v>27.5886</v>
       </c>
       <c r="H244">
-        <v>202.76412</v>
+        <v>202.7641215</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -10800,7 +10800,7 @@
         <v>28.67899</v>
       </c>
       <c r="H245">
-        <v>209.17733</v>
+        <v>209.1773255</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -10826,7 +10826,7 @@
         <v>31.49325</v>
       </c>
       <c r="H246">
-        <v>273.82163</v>
+        <v>273.8216295</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -10852,7 +10852,7 @@
         <v>6.8296</v>
       </c>
       <c r="H247">
-        <v>93.66125</v>
+        <v>93.66125211000001</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -10878,7 +10878,7 @@
         <v>11.19052</v>
       </c>
       <c r="H248">
-        <v>102.71032</v>
+        <v>150.6651543</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -10904,7 +10904,7 @@
         <v>15.30579</v>
       </c>
       <c r="H249">
-        <v>133.85874</v>
+        <v>133.8587442</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -10930,7 +10930,7 @@
         <v>11.11968</v>
       </c>
       <c r="H250">
-        <v>97.9644</v>
+        <v>97.96439771</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -10956,7 +10956,7 @@
         <v>21.364</v>
       </c>
       <c r="H251">
-        <v>181.66553</v>
+        <v>181.6655286</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -10982,7 +10982,7 @@
         <v>21.04704</v>
       </c>
       <c r="H252">
-        <v>169.36902</v>
+        <v>169.3690217</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -11008,7 +11008,7 @@
         <v>24.26222</v>
       </c>
       <c r="H253">
-        <v>200.08711</v>
+        <v>200.0871134</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -11034,7 +11034,7 @@
         <v>28.65597</v>
       </c>
       <c r="H254">
-        <v>194.80322</v>
+        <v>194.8032169</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -11060,7 +11060,7 @@
         <v>23.8377</v>
       </c>
       <c r="H255">
-        <v>194.60509</v>
+        <v>194.6050897</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -11086,7 +11086,7 @@
         <v>27.39768</v>
       </c>
       <c r="H256">
-        <v>212.52203</v>
+        <v>212.5220332</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -11112,7 +11112,7 @@
         <v>19.79247</v>
       </c>
       <c r="H257">
-        <v>141.39002</v>
+        <v>141.3900188</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -11138,7 +11138,7 @@
         <v>21.92947</v>
       </c>
       <c r="H258">
-        <v>210.75666</v>
+        <v>210.7566593</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -11164,7 +11164,7 @@
         <v>14.3724</v>
       </c>
       <c r="H259">
-        <v>111.9139</v>
+        <v>111.9139013</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -11190,7 +11190,7 @@
         <v>104.70128</v>
       </c>
       <c r="H260">
-        <v>360.57695</v>
+        <v>360.5769545</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -11216,7 +11216,7 @@
         <v>14.40205</v>
       </c>
       <c r="H261">
-        <v>139.33181</v>
+        <v>139.3318091</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -11242,7 +11242,7 @@
         <v>56.17111</v>
       </c>
       <c r="H262">
-        <v>293.90013</v>
+        <v>293.9001276</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -11268,7 +11268,7 @@
         <v>46.31326</v>
       </c>
       <c r="H263">
-        <v>228.42791</v>
+        <v>228.427909</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -11294,7 +11294,7 @@
         <v>58.01217</v>
       </c>
       <c r="H264">
-        <v>312.89654</v>
+        <v>312.896543</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -11320,7 +11320,7 @@
         <v>12.89297</v>
       </c>
       <c r="H265">
-        <v>161.75729</v>
+        <v>161.7572853</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -11346,7 +11346,7 @@
         <v>15.14393</v>
       </c>
       <c r="H266">
-        <v>195.36397</v>
+        <v>195.3639655</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -11372,7 +11372,7 @@
         <v>10.54702</v>
       </c>
       <c r="H267">
-        <v>139.95822</v>
+        <v>139.958223</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -11398,7 +11398,7 @@
         <v>29.4381</v>
       </c>
       <c r="H268">
-        <v>331.31312</v>
+        <v>331.3131151</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -11424,7 +11424,7 @@
         <v>17.69394</v>
       </c>
       <c r="H269">
-        <v>138.51281</v>
+        <v>138.5128082</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -11450,7 +11450,7 @@
         <v>24.21352</v>
       </c>
       <c r="H270">
-        <v>203.81089</v>
+        <v>203.8108907</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -11476,7 +11476,7 @@
         <v>18.54039</v>
       </c>
       <c r="H271">
-        <v>119.73781</v>
+        <v>119.7378124</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -11502,7 +11502,7 @@
         <v>26.33793</v>
       </c>
       <c r="H272">
-        <v>155.14563</v>
+        <v>155.1456261</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -11528,7 +11528,7 @@
         <v>15.46336</v>
       </c>
       <c r="H273">
-        <v>167.23912</v>
+        <v>167.2391214</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -11554,7 +11554,7 @@
         <v>24.57541</v>
       </c>
       <c r="H274">
-        <v>247.49564</v>
+        <v>247.4956416</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -11580,7 +11580,7 @@
         <v>43.2619</v>
       </c>
       <c r="H275">
-        <v>259.79134</v>
+        <v>259.7913416</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -11606,7 +11606,7 @@
         <v>14.19513</v>
       </c>
       <c r="H276">
-        <v>130.43495</v>
+        <v>130.4349519</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -11632,7 +11632,7 @@
         <v>9.200799999999999</v>
       </c>
       <c r="H277">
-        <v>101.78058</v>
+        <v>101.7805847</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -11658,7 +11658,7 @@
         <v>104.95251</v>
       </c>
       <c r="H278">
-        <v>582.4398</v>
+        <v>582.4398034</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -11684,7 +11684,7 @@
         <v>21.29618</v>
       </c>
       <c r="H279">
-        <v>198.44851</v>
+        <v>174.126788</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -11710,7 +11710,7 @@
         <v>19.64944</v>
       </c>
       <c r="H280">
-        <v>164.98426</v>
+        <v>133.2565866</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -11736,7 +11736,7 @@
         <v>73.38531999999999</v>
       </c>
       <c r="H281">
-        <v>332.3865</v>
+        <v>422.7335572</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -11762,7 +11762,7 @@
         <v>26.40989</v>
       </c>
       <c r="H282">
-        <v>182.26969</v>
+        <v>182.2696921</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -11788,7 +11788,7 @@
         <v>32.64263</v>
       </c>
       <c r="H283">
-        <v>153.89572</v>
+        <v>155.5589575</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -11814,7 +11814,7 @@
         <v>37.65374</v>
       </c>
       <c r="H284">
-        <v>190.8109</v>
+        <v>183.2478962</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -11840,7 +11840,7 @@
         <v>1.51224</v>
       </c>
       <c r="H285">
-        <v>39.76958</v>
+        <v>39.76957589</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -11866,7 +11866,7 @@
         <v>38.854</v>
       </c>
       <c r="H286">
-        <v>211.73186</v>
+        <v>211.7318627</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -11892,7 +11892,7 @@
         <v>33.95902</v>
       </c>
       <c r="H287">
-        <v>172.07267</v>
+        <v>179.9622569</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -11918,7 +11918,7 @@
         <v>41.74523</v>
       </c>
       <c r="H288">
-        <v>230.39107</v>
+        <v>229.6087371</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -11944,7 +11944,7 @@
         <v>45.62153</v>
       </c>
       <c r="H289">
-        <v>236.54346</v>
+        <v>242.284697</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -11970,7 +11970,7 @@
         <v>33.45485</v>
       </c>
       <c r="H290">
-        <v>151.30283</v>
+        <v>151.3028282</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -11996,7 +11996,7 @@
         <v>42.72015</v>
       </c>
       <c r="H291">
-        <v>195.81927</v>
+        <v>195.8192744</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -12022,7 +12022,7 @@
         <v>19.27066</v>
       </c>
       <c r="H292">
-        <v>407.82446</v>
+        <v>407.8244578</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -12048,7 +12048,7 @@
         <v>22.09822</v>
       </c>
       <c r="H293">
-        <v>195.80731</v>
+        <v>225.5577547</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -12074,7 +12074,7 @@
         <v>16.3387</v>
       </c>
       <c r="H294">
-        <v>141.45124</v>
+        <v>221.6959732</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -12100,7 +12100,7 @@
         <v>4.156</v>
       </c>
       <c r="H295">
-        <v>55.87359</v>
+        <v>85.19756388</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -12126,7 +12126,7 @@
         <v>5.4875</v>
       </c>
       <c r="H296">
-        <v>59.45624</v>
+        <v>137.1134592</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -12152,7 +12152,7 @@
         <v>7.72804</v>
       </c>
       <c r="H297">
-        <v>90.8477</v>
+        <v>90.84770278000001</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -12178,7 +12178,7 @@
         <v>4.12542</v>
       </c>
       <c r="H298">
-        <v>54.35174</v>
+        <v>54.35174312</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -12204,7 +12204,7 @@
         <v>6.39219</v>
       </c>
       <c r="H299">
-        <v>92.54528000000001</v>
+        <v>92.54527869</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -12230,7 +12230,7 @@
         <v>4.35413</v>
       </c>
       <c r="H300">
-        <v>57.49113</v>
+        <v>57.49112625</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -12256,7 +12256,7 @@
         <v>17.75899</v>
       </c>
       <c r="H301">
-        <v>152.22204</v>
+        <v>152.2220401</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -12282,7 +12282,7 @@
         <v>18.36595</v>
       </c>
       <c r="H302">
-        <v>135.11678</v>
+        <v>135.1167812</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -12308,7 +12308,7 @@
         <v>23.03515</v>
       </c>
       <c r="H303">
-        <v>179.75862</v>
+        <v>179.7586197</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -12334,7 +12334,7 @@
         <v>11.74373</v>
       </c>
       <c r="H304">
-        <v>106.44567</v>
+        <v>106.4456693</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -12360,7 +12360,7 @@
         <v>11.99654</v>
       </c>
       <c r="H305">
-        <v>126.65756</v>
+        <v>126.6575558</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -12386,7 +12386,7 @@
         <v>7.35653</v>
       </c>
       <c r="H306">
-        <v>74.75519</v>
+        <v>74.75519359</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -12412,7 +12412,7 @@
         <v>5.21915</v>
       </c>
       <c r="H307">
-        <v>70.8653</v>
+        <v>70.86529935</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -12438,7 +12438,7 @@
         <v>2.76762</v>
       </c>
       <c r="H308">
-        <v>43.81443</v>
+        <v>43.81443412</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -12464,7 +12464,7 @@
         <v>12.62277</v>
       </c>
       <c r="H309">
-        <v>134.54507</v>
+        <v>134.5450689</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -12490,7 +12490,7 @@
         <v>10.23247</v>
       </c>
       <c r="H310">
-        <v>102.70287</v>
+        <v>190.3763253</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -12516,7 +12516,7 @@
         <v>12.69278</v>
       </c>
       <c r="H311">
-        <v>137.05821</v>
+        <v>137.0582068</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -12542,7 +12542,7 @@
         <v>6.00005</v>
       </c>
       <c r="H312">
-        <v>76.19264</v>
+        <v>76.19263771999999</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -12568,7 +12568,7 @@
         <v>4.81468</v>
       </c>
       <c r="H313">
-        <v>61.16178</v>
+        <v>61.16177612</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -12594,7 +12594,7 @@
         <v>7.71228</v>
       </c>
       <c r="H314">
-        <v>111.97868</v>
+        <v>111.9786841</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -12620,7 +12620,7 @@
         <v>5.58342</v>
       </c>
       <c r="H315">
-        <v>72.47302000000001</v>
+        <v>72.47302492</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -12646,7 +12646,7 @@
         <v>6.3612</v>
       </c>
       <c r="H316">
-        <v>92.79604999999999</v>
+        <v>92.79604756000001</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -12672,7 +12672,7 @@
         <v>5.58113</v>
       </c>
       <c r="H317">
-        <v>66.09184999999999</v>
+        <v>66.09185101999999</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -12698,7 +12698,7 @@
         <v>4.70535</v>
       </c>
       <c r="H318">
-        <v>61.7299</v>
+        <v>61.72990149</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -12724,7 +12724,7 @@
         <v>4.55268</v>
       </c>
       <c r="H319">
-        <v>67.21234</v>
+        <v>67.21234407</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -12750,7 +12750,7 @@
         <v>4.33346</v>
       </c>
       <c r="H320">
-        <v>59.09757</v>
+        <v>59.09757014</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -12776,7 +12776,7 @@
         <v>4.38136</v>
       </c>
       <c r="H321">
-        <v>60.32921</v>
+        <v>60.32921383</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -12802,7 +12802,7 @@
         <v>94.53899</v>
       </c>
       <c r="H322">
-        <v>271.93709</v>
+        <v>271.9370899</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -12828,7 +12828,7 @@
         <v>9.440630000000001</v>
       </c>
       <c r="H323">
-        <v>97.40358999999999</v>
+        <v>97.40358719</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -12854,7 +12854,7 @@
         <v>20.75674</v>
       </c>
       <c r="H324">
-        <v>182.42435</v>
+        <v>182.4243518</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -12880,7 +12880,7 @@
         <v>6.63301</v>
       </c>
       <c r="H325">
-        <v>98.25924999999999</v>
+        <v>98.25925257</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -12906,7 +12906,7 @@
         <v>4.6109</v>
       </c>
       <c r="H326">
-        <v>60.82922</v>
+        <v>60.82921555</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -12932,7 +12932,7 @@
         <v>6.16472</v>
       </c>
       <c r="H327">
-        <v>70.76927999999999</v>
+        <v>70.76927954999999</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -12958,7 +12958,7 @@
         <v>4.74954</v>
       </c>
       <c r="H328">
-        <v>60.67894</v>
+        <v>60.67894302</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -12984,7 +12984,7 @@
         <v>7.65913</v>
       </c>
       <c r="H329">
-        <v>101.65617</v>
+        <v>101.6561747</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -13010,7 +13010,7 @@
         <v>6.18382</v>
       </c>
       <c r="H330">
-        <v>72.77954</v>
+        <v>72.77953608</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -13036,7 +13036,7 @@
         <v>0.94256</v>
       </c>
       <c r="H331">
-        <v>34.72999</v>
+        <v>34.72998962</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -13062,7 +13062,7 @@
         <v>31.40937</v>
       </c>
       <c r="H332">
-        <v>175.94988</v>
+        <v>105.2392575</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -13088,7 +13088,7 @@
         <v>27.08978</v>
       </c>
       <c r="H333">
-        <v>379.88153</v>
+        <v>379.8815307</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -13114,7 +13114,7 @@
         <v>11.49974</v>
       </c>
       <c r="H334">
-        <v>195.02577</v>
+        <v>195.0257651</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -13140,7 +13140,7 @@
         <v>107.33899</v>
       </c>
       <c r="H335">
-        <v>338.5038</v>
+        <v>338.5037979</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -13166,7 +13166,7 @@
         <v>55.2916</v>
       </c>
       <c r="H336">
-        <v>271.73171</v>
+        <v>196.6727312</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -13192,7 +13192,7 @@
         <v>61.63347</v>
       </c>
       <c r="H337">
-        <v>339.85447</v>
+        <v>339.854474</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -13218,7 +13218,7 @@
         <v>65.86317</v>
       </c>
       <c r="H338">
-        <v>377.76598</v>
+        <v>377.7659762</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -13244,7 +13244,7 @@
         <v>19.19395</v>
       </c>
       <c r="H339">
-        <v>119.74584</v>
+        <v>119.7458381</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -13270,7 +13270,7 @@
         <v>16.73486</v>
       </c>
       <c r="H340">
-        <v>119.39729</v>
+        <v>125.4778286</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -13296,7 +13296,7 @@
         <v>67.74921000000001</v>
       </c>
       <c r="H341">
-        <v>321.17264</v>
+        <v>267.905585</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -13322,7 +13322,7 @@
         <v>62.80032</v>
       </c>
       <c r="H342">
-        <v>265.92291</v>
+        <v>256.3762051</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -13348,7 +13348,7 @@
         <v>19.08898</v>
       </c>
       <c r="H343">
-        <v>139.98205</v>
+        <v>110.114447</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -13374,7 +13374,7 @@
         <v>45.19574</v>
       </c>
       <c r="H344">
-        <v>198.87131</v>
+        <v>226.4026459</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -13400,7 +13400,7 @@
         <v>109.4403</v>
       </c>
       <c r="H345">
-        <v>531.39013</v>
+        <v>531.3901311</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -13426,7 +13426,7 @@
         <v>86.41046</v>
       </c>
       <c r="H346">
-        <v>407.02738</v>
+        <v>407.0273764</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -13452,7 +13452,7 @@
         <v>58.19802</v>
       </c>
       <c r="H347">
-        <v>216.80821</v>
+        <v>216.8082094</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -13478,7 +13478,7 @@
         <v>35.85461</v>
       </c>
       <c r="H348">
-        <v>200.09036</v>
+        <v>200.0903559</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -13504,7 +13504,7 @@
         <v>66.95801</v>
       </c>
       <c r="H349">
-        <v>355.23317</v>
+        <v>355.2331657</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -13530,7 +13530,7 @@
         <v>60.20097</v>
       </c>
       <c r="H350">
-        <v>280.89631</v>
+        <v>280.8963059</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -13556,7 +13556,7 @@
         <v>40.6303</v>
       </c>
       <c r="H351">
-        <v>199.34632</v>
+        <v>199.3463239</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -13582,7 +13582,7 @@
         <v>103.84344</v>
       </c>
       <c r="H352">
-        <v>446.18832</v>
+        <v>369.8839433</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -13608,7 +13608,7 @@
         <v>82.01737</v>
       </c>
       <c r="H353">
-        <v>439.38132</v>
+        <v>439.3813216</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -13634,7 +13634,7 @@
         <v>14.71466</v>
       </c>
       <c r="H354">
-        <v>160.7827</v>
+        <v>160.7826971</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -13686,7 +13686,7 @@
         <v>11.7943</v>
       </c>
       <c r="H356">
-        <v>153.4898</v>
+        <v>153.4897994</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -13712,7 +13712,7 @@
         <v>53.08823</v>
       </c>
       <c r="H357">
-        <v>285.63146</v>
+        <v>285.6314619</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -13738,7 +13738,7 @@
         <v>66.0371</v>
       </c>
       <c r="H358">
-        <v>418.18695</v>
+        <v>418.1869466</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -13764,7 +13764,7 @@
         <v>75.49171</v>
       </c>
       <c r="H359">
-        <v>299.1052</v>
+        <v>271.3262422</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -13790,7 +13790,7 @@
         <v>31.284</v>
       </c>
       <c r="H360">
-        <v>192.38521</v>
+        <v>192.3852083</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -13816,7 +13816,7 @@
         <v>11.56472</v>
       </c>
       <c r="H361">
-        <v>125.32023</v>
+        <v>187.12296</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -13842,7 +13842,7 @@
         <v>10.41664</v>
       </c>
       <c r="H362">
-        <v>86.19741999999999</v>
+        <v>88.68395798</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -13868,7 +13868,7 @@
         <v>13.38834</v>
       </c>
       <c r="H363">
-        <v>129.53353</v>
+        <v>129.5335264</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -13894,7 +13894,7 @@
         <v>42.88406</v>
       </c>
       <c r="H364">
-        <v>246.95028</v>
+        <v>246.9502761</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -13920,7 +13920,7 @@
         <v>34.76224</v>
       </c>
       <c r="H365">
-        <v>202.01752</v>
+        <v>202.0175246</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -13946,7 +13946,7 @@
         <v>20.42807</v>
       </c>
       <c r="H366">
-        <v>173.66292</v>
+        <v>173.6629215</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -13972,7 +13972,7 @@
         <v>22.67722</v>
       </c>
       <c r="H367">
-        <v>148.54499</v>
+        <v>128.6055791</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -13998,7 +13998,7 @@
         <v>23.88861</v>
       </c>
       <c r="H368">
-        <v>169.04086</v>
+        <v>168.4072886</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -14024,7 +14024,7 @@
         <v>24.86732</v>
       </c>
       <c r="H369">
-        <v>186.41356</v>
+        <v>175.4161264</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -14050,7 +14050,7 @@
         <v>44.50569</v>
       </c>
       <c r="H370">
-        <v>233.72899</v>
+        <v>282.9599898</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -14076,7 +14076,7 @@
         <v>33.88314</v>
       </c>
       <c r="H371">
-        <v>228.59291</v>
+        <v>256.3479099</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -14102,7 +14102,7 @@
         <v>45.15584</v>
       </c>
       <c r="H372">
-        <v>261.73659</v>
+        <v>307.2108322</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -14128,7 +14128,7 @@
         <v>20.58529</v>
       </c>
       <c r="H373">
-        <v>144.90748</v>
+        <v>144.9074807</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -14154,7 +14154,7 @@
         <v>42.57532</v>
       </c>
       <c r="H374">
-        <v>245.45509</v>
+        <v>271.3517852</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -14180,7 +14180,7 @@
         <v>11.40524</v>
       </c>
       <c r="H375">
-        <v>113.30516</v>
+        <v>155.5273349</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -14206,7 +14206,7 @@
         <v>17.27313</v>
       </c>
       <c r="H376">
-        <v>153.39917</v>
+        <v>153.399171</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -14232,7 +14232,7 @@
         <v>12.40742</v>
       </c>
       <c r="H377">
-        <v>101.94273</v>
+        <v>124.9806194</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -14258,7 +14258,7 @@
         <v>12.0903</v>
       </c>
       <c r="H378">
-        <v>116.30994</v>
+        <v>207.3080566</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -14284,7 +14284,7 @@
         <v>10.14692</v>
       </c>
       <c r="H379">
-        <v>83.30218000000001</v>
+        <v>120.3172501</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -14310,7 +14310,7 @@
         <v>26.5503</v>
       </c>
       <c r="H380">
-        <v>179.67683</v>
+        <v>179.6768319</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -14336,7 +14336,7 @@
         <v>12.78911</v>
       </c>
       <c r="H381">
-        <v>132.09525</v>
+        <v>185.5953619</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -14362,7 +14362,7 @@
         <v>17.34749</v>
       </c>
       <c r="H382">
-        <v>163.13826</v>
+        <v>163.1382576</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -14388,7 +14388,7 @@
         <v>10.89464</v>
       </c>
       <c r="H383">
-        <v>100.5436</v>
+        <v>132.0233782</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -14414,7 +14414,7 @@
         <v>10.31424</v>
       </c>
       <c r="H384">
-        <v>114.51646</v>
+        <v>198.2452317</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -14440,7 +14440,7 @@
         <v>9.8978</v>
       </c>
       <c r="H385">
-        <v>85.97801</v>
+        <v>95.47625861</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -14466,7 +14466,7 @@
         <v>9.953060000000001</v>
       </c>
       <c r="H386">
-        <v>85.77882</v>
+        <v>96.78025863000001</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -14492,7 +14492,7 @@
         <v>10.69839</v>
       </c>
       <c r="H387">
-        <v>122.48343</v>
+        <v>122.4834329</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -14518,7 +14518,7 @@
         <v>12.56531</v>
       </c>
       <c r="H388">
-        <v>100.70141</v>
+        <v>100.7014132</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -14544,7 +14544,7 @@
         <v>29.58629</v>
       </c>
       <c r="H389">
-        <v>172.81835</v>
+        <v>172.8183472</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -14570,7 +14570,7 @@
         <v>13.37381</v>
       </c>
       <c r="H390">
-        <v>133.9327</v>
+        <v>192.5046096</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -14596,7 +14596,7 @@
         <v>25.66613</v>
       </c>
       <c r="H391">
-        <v>162.61385</v>
+        <v>141.4191883</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -14622,7 +14622,7 @@
         <v>76.94705</v>
       </c>
       <c r="H392">
-        <v>281.65368</v>
+        <v>281.6536778</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -14648,7 +14648,7 @@
         <v>36.03314</v>
       </c>
       <c r="H393">
-        <v>164.22052</v>
+        <v>255.3387239</v>
       </c>
     </row>
     <row r="394" spans="1:8">
@@ -14674,7 +14674,7 @@
         <v>15.47876</v>
       </c>
       <c r="H394">
-        <v>177.34386</v>
+        <v>177.3438631</v>
       </c>
     </row>
     <row r="395" spans="1:8">
@@ -14700,7 +14700,7 @@
         <v>68.46973</v>
       </c>
       <c r="H395">
-        <v>423.52945</v>
+        <v>428.4844845</v>
       </c>
     </row>
     <row r="396" spans="1:8">
@@ -14726,7 +14726,7 @@
         <v>60.96248</v>
       </c>
       <c r="H396">
-        <v>374.09517</v>
+        <v>374.0951738</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -14752,7 +14752,7 @@
         <v>52.49257</v>
       </c>
       <c r="H397">
-        <v>324.23874</v>
+        <v>324.2387397</v>
       </c>
     </row>
     <row r="398" spans="1:8">
@@ -14778,7 +14778,7 @@
         <v>57.84917</v>
       </c>
       <c r="H398">
-        <v>342.43292</v>
+        <v>342.4329177</v>
       </c>
     </row>
     <row r="399" spans="1:8">
@@ -14804,7 +14804,7 @@
         <v>59.21404</v>
       </c>
       <c r="H399">
-        <v>386.90217</v>
+        <v>386.9021748</v>
       </c>
     </row>
     <row r="400" spans="1:8">
@@ -14830,7 +14830,7 @@
         <v>46.57928</v>
       </c>
       <c r="H400">
-        <v>272.33066</v>
+        <v>272.3306555</v>
       </c>
     </row>
     <row r="401" spans="1:8">
@@ -14856,7 +14856,7 @@
         <v>13.8101</v>
       </c>
       <c r="H401">
-        <v>116.11822</v>
+        <v>116.1182177</v>
       </c>
     </row>
     <row r="402" spans="1:8">
@@ -14882,7 +14882,7 @@
         <v>16.41724</v>
       </c>
       <c r="H402">
-        <v>170.68713</v>
+        <v>212.0663262</v>
       </c>
     </row>
     <row r="403" spans="1:8">
@@ -14908,7 +14908,7 @@
         <v>15.4105</v>
       </c>
       <c r="H403">
-        <v>123.1356</v>
+        <v>123.1356037</v>
       </c>
     </row>
     <row r="404" spans="1:8">
@@ -14934,7 +14934,7 @@
         <v>16.94675</v>
       </c>
       <c r="H404">
-        <v>157.08182</v>
+        <v>157.0818226</v>
       </c>
     </row>
     <row r="405" spans="1:8">
@@ -14960,7 +14960,7 @@
         <v>13.55357</v>
       </c>
       <c r="H405">
-        <v>116.57403</v>
+        <v>116.5740335</v>
       </c>
     </row>
     <row r="406" spans="1:8">
@@ -14986,7 +14986,7 @@
         <v>16.53267</v>
       </c>
       <c r="H406">
-        <v>157.78294</v>
+        <v>157.782936</v>
       </c>
     </row>
     <row r="407" spans="1:8">
@@ -15012,7 +15012,7 @@
         <v>13.05565</v>
       </c>
       <c r="H407">
-        <v>123.63305</v>
+        <v>123.6330487</v>
       </c>
     </row>
     <row r="408" spans="1:8">
@@ -15038,7 +15038,7 @@
         <v>14.71721</v>
       </c>
       <c r="H408">
-        <v>163.79326</v>
+        <v>163.7932555</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -15064,7 +15064,7 @@
         <v>13.96478</v>
       </c>
       <c r="H409">
-        <v>156.27866</v>
+        <v>156.2786564</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -15090,7 +15090,7 @@
         <v>14.84912</v>
       </c>
       <c r="H410">
-        <v>175.40132</v>
+        <v>175.401321</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -15116,7 +15116,7 @@
         <v>13.2919</v>
       </c>
       <c r="H411">
-        <v>139.53163</v>
+        <v>139.5316301</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -15142,7 +15142,7 @@
         <v>40.29939</v>
       </c>
       <c r="H412">
-        <v>261.31812</v>
+        <v>261.3181169</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -15168,7 +15168,7 @@
         <v>55.16004</v>
       </c>
       <c r="H413">
-        <v>323.4751</v>
+        <v>323.4750967</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -15194,7 +15194,7 @@
         <v>27.13368</v>
       </c>
       <c r="H414">
-        <v>167.27994</v>
+        <v>167.2799382</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -15220,7 +15220,7 @@
         <v>36.85011</v>
       </c>
       <c r="H415">
-        <v>189.07424</v>
+        <v>189.0742355</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -15246,7 +15246,7 @@
         <v>26.3309</v>
       </c>
       <c r="H416">
-        <v>281.63915</v>
+        <v>281.6391465</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -15272,7 +15272,7 @@
         <v>48.16614</v>
       </c>
       <c r="H417">
-        <v>223.62112</v>
+        <v>223.6211152</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -15298,7 +15298,7 @@
         <v>46.53017</v>
       </c>
       <c r="H418">
-        <v>215.58016</v>
+        <v>215.5801572</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -15324,7 +15324,7 @@
         <v>65.09184</v>
       </c>
       <c r="H419">
-        <v>228.83588</v>
+        <v>240.1408445</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -15350,7 +15350,7 @@
         <v>21.22247</v>
       </c>
       <c r="H420">
-        <v>183.39167</v>
+        <v>183.3916675</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -15376,7 +15376,7 @@
         <v>28.5584</v>
       </c>
       <c r="H421">
-        <v>200.08761</v>
+        <v>200.0876149</v>
       </c>
     </row>
     <row r="422" spans="1:8">
@@ -15402,7 +15402,7 @@
         <v>25.9447</v>
       </c>
       <c r="H422">
-        <v>199.57968</v>
+        <v>199.5796812</v>
       </c>
     </row>
     <row r="423" spans="1:8">
@@ -15428,7 +15428,7 @@
         <v>13.67125</v>
       </c>
       <c r="H423">
-        <v>149.34046</v>
+        <v>149.3404644</v>
       </c>
     </row>
     <row r="424" spans="1:8">
@@ -15454,7 +15454,7 @@
         <v>49.15856</v>
       </c>
       <c r="H424">
-        <v>292.9153</v>
+        <v>278.1479183</v>
       </c>
     </row>
     <row r="425" spans="1:8">
@@ -15480,7 +15480,7 @@
         <v>42.09523</v>
       </c>
       <c r="H425">
-        <v>237.42053</v>
+        <v>237.4205283</v>
       </c>
     </row>
     <row r="426" spans="1:8">
@@ -15506,7 +15506,7 @@
         <v>50.01696</v>
       </c>
       <c r="H426">
-        <v>268.57673</v>
+        <v>268.5767294</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -15532,7 +15532,7 @@
         <v>52.41746</v>
       </c>
       <c r="H427">
-        <v>288.5919</v>
+        <v>288.5918964</v>
       </c>
     </row>
     <row r="428" spans="1:8">
@@ -15558,7 +15558,7 @@
         <v>53.91355</v>
       </c>
       <c r="H428">
-        <v>293.47038</v>
+        <v>386.549863</v>
       </c>
     </row>
     <row r="429" spans="1:8">
@@ -15610,7 +15610,7 @@
         <v>44.42624</v>
       </c>
       <c r="H430">
-        <v>266.07565</v>
+        <v>266.0756498</v>
       </c>
     </row>
     <row r="431" spans="1:8">
@@ -15636,7 +15636,7 @@
         <v>45.61612</v>
       </c>
       <c r="H431">
-        <v>245.9616</v>
+        <v>245.9616041</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -15662,7 +15662,7 @@
         <v>12.64956</v>
       </c>
       <c r="H432">
-        <v>111.99255</v>
+        <v>157.2497733</v>
       </c>
     </row>
     <row r="433" spans="1:8">
@@ -15688,7 +15688,7 @@
         <v>15.28429</v>
       </c>
       <c r="H433">
-        <v>150.55169</v>
+        <v>216.3147367</v>
       </c>
     </row>
     <row r="434" spans="1:8">
@@ -15714,7 +15714,7 @@
         <v>20.41585</v>
       </c>
       <c r="H434">
-        <v>182.54005</v>
+        <v>182.5400511</v>
       </c>
     </row>
     <row r="435" spans="1:8">
@@ -15740,7 +15740,7 @@
         <v>10.24668</v>
       </c>
       <c r="H435">
-        <v>85.59101</v>
+        <v>85.59101122</v>
       </c>
     </row>
     <row r="436" spans="1:8">
@@ -15766,7 +15766,7 @@
         <v>21.30508</v>
       </c>
       <c r="H436">
-        <v>202.53367</v>
+        <v>202.5336688</v>
       </c>
     </row>
     <row r="437" spans="1:8">
@@ -15792,7 +15792,7 @@
         <v>12.06511</v>
       </c>
       <c r="H437">
-        <v>109.8277</v>
+        <v>109.8277047</v>
       </c>
     </row>
     <row r="438" spans="1:8">
@@ -15818,7 +15818,7 @@
         <v>13.24102</v>
       </c>
       <c r="H438">
-        <v>139.3349</v>
+        <v>139.3349001</v>
       </c>
     </row>
     <row r="439" spans="1:8">
@@ -15844,7 +15844,7 @@
         <v>12.88238</v>
       </c>
       <c r="H439">
-        <v>147.13713</v>
+        <v>220.3832424</v>
       </c>
     </row>
     <row r="440" spans="1:8">
@@ -15870,7 +15870,7 @@
         <v>11.4439</v>
       </c>
       <c r="H440">
-        <v>101.58696</v>
+        <v>101.586961</v>
       </c>
     </row>
     <row r="441" spans="1:8">
@@ -15896,7 +15896,7 @@
         <v>12.77462</v>
       </c>
       <c r="H441">
-        <v>126.83754</v>
+        <v>126.8375434</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -15922,7 +15922,7 @@
         <v>13.7127</v>
       </c>
       <c r="H442">
-        <v>145.97542</v>
+        <v>145.9754195</v>
       </c>
     </row>
     <row r="443" spans="1:8">
@@ -15948,7 +15948,7 @@
         <v>34.16358</v>
       </c>
       <c r="H443">
-        <v>220.71654</v>
+        <v>159.3591017</v>
       </c>
     </row>
     <row r="444" spans="1:8">
@@ -15974,7 +15974,7 @@
         <v>38.43016</v>
       </c>
       <c r="H444">
-        <v>238.88403</v>
+        <v>215.4415547</v>
       </c>
     </row>
     <row r="445" spans="1:8">
@@ -16000,7 +16000,7 @@
         <v>16.17742</v>
       </c>
       <c r="H445">
-        <v>117.96834</v>
+        <v>117.968341</v>
       </c>
     </row>
     <row r="446" spans="1:8">
@@ -16026,7 +16026,7 @@
         <v>14.68835</v>
       </c>
       <c r="H446">
-        <v>119.65154</v>
+        <v>119.6515368</v>
       </c>
     </row>
     <row r="447" spans="1:8">
@@ -16052,7 +16052,7 @@
         <v>14.09164</v>
       </c>
       <c r="H447">
-        <v>110.05797</v>
+        <v>110.0579722</v>
       </c>
     </row>
     <row r="448" spans="1:8">
@@ -16078,7 +16078,7 @@
         <v>15.47238</v>
       </c>
       <c r="H448">
-        <v>92.1427</v>
+        <v>64.56154755999999</v>
       </c>
     </row>
     <row r="449" spans="1:8">
@@ -16104,7 +16104,7 @@
         <v>23.84089</v>
       </c>
       <c r="H449">
-        <v>134.87662</v>
+        <v>134.8766196</v>
       </c>
     </row>
     <row r="450" spans="1:8">
@@ -16130,7 +16130,7 @@
         <v>65.75790000000001</v>
       </c>
       <c r="H450">
-        <v>281.43649</v>
+        <v>281.4364857</v>
       </c>
     </row>
     <row r="451" spans="1:8">
@@ -16156,7 +16156,7 @@
         <v>98.12275</v>
       </c>
       <c r="H451">
-        <v>482.70765</v>
+        <v>469.347036</v>
       </c>
     </row>
     <row r="452" spans="1:8">
@@ -16182,7 +16182,7 @@
         <v>10.3716</v>
       </c>
       <c r="H452">
-        <v>89.89857000000001</v>
+        <v>92.44440536</v>
       </c>
     </row>
     <row r="453" spans="1:8">
@@ -16208,7 +16208,7 @@
         <v>18.90669</v>
       </c>
       <c r="H453">
-        <v>166.84659</v>
+        <v>140.9891682</v>
       </c>
     </row>
     <row r="454" spans="1:8">
@@ -16234,7 +16234,7 @@
         <v>23.21781</v>
       </c>
       <c r="H454">
-        <v>227.88077</v>
+        <v>210.3599667</v>
       </c>
     </row>
     <row r="455" spans="1:8">
@@ -16260,7 +16260,7 @@
         <v>42.65308</v>
       </c>
       <c r="H455">
-        <v>322.45349</v>
+        <v>285.1996394</v>
       </c>
     </row>
     <row r="456" spans="1:8">
@@ -16286,7 +16286,7 @@
         <v>14.34671</v>
       </c>
       <c r="H456">
-        <v>127.07575</v>
+        <v>102.0782558</v>
       </c>
     </row>
     <row r="457" spans="1:8">
@@ -16312,7 +16312,7 @@
         <v>121.04356</v>
       </c>
       <c r="H457">
-        <v>716.2033699999999</v>
+        <v>662.1877077</v>
       </c>
     </row>
     <row r="458" spans="1:8">
@@ -16338,7 +16338,7 @@
         <v>28.36043</v>
       </c>
       <c r="H458">
-        <v>208.87336</v>
+        <v>174.0633073</v>
       </c>
     </row>
     <row r="459" spans="1:8">
@@ -16364,7 +16364,7 @@
         <v>35.7164</v>
       </c>
       <c r="H459">
-        <v>302.80342</v>
+        <v>284.3563001</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -16390,7 +16390,7 @@
         <v>74.32163</v>
       </c>
       <c r="H460">
-        <v>469.96186</v>
+        <v>440.857096</v>
       </c>
     </row>
     <row r="461" spans="1:8">
@@ -16416,7 +16416,7 @@
         <v>21.05754</v>
       </c>
       <c r="H461">
-        <v>154.67907</v>
+        <v>115.5546656</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -16442,7 +16442,7 @@
         <v>83.53493</v>
       </c>
       <c r="H462">
-        <v>362.72479</v>
+        <v>305.7287475</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -16468,7 +16468,7 @@
         <v>40.88708</v>
       </c>
       <c r="H463">
-        <v>301.91604</v>
+        <v>255.832082</v>
       </c>
     </row>
     <row r="464" spans="1:8">
